--- a/AccessDBs/Архипов/Архипов Нормализация в2.xlsx
+++ b/AccessDBs/Архипов/Архипов Нормализация в2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CollegeStudy\AccessDBs\Архипов\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeWriting\Projects\CollegeStudy\AccessDBs\Архипов\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472CF8D1-25C9-44E7-88D3-A19712AEB484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E286BB-8ADD-43A1-B707-CED8EC08D012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1NF" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -330,9 +327,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -342,7 +338,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -354,22 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -828,321 +818,321 @@
   </cols>
   <sheetData>
     <row r="3" spans="10:18" x14ac:dyDescent="0.25">
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="10:18" x14ac:dyDescent="0.25">
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>1</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="1">
         <v>15</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="O4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>10</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>8.6999999999999993</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="1">
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="10:18" x14ac:dyDescent="0.25">
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>2</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <v>20</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>30</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>9.1999999999999993</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="1">
         <v>280</v>
       </c>
     </row>
     <row r="6" spans="10:18" x14ac:dyDescent="0.25">
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>3</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="1">
         <v>25</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="N6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>60</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>10.4</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="1">
         <v>620</v>
       </c>
     </row>
     <row r="7" spans="10:18" x14ac:dyDescent="0.25">
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <v>4</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <v>32</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="N7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="O7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>20</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>11.5</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="1">
         <v>230</v>
       </c>
     </row>
     <row r="8" spans="10:18" x14ac:dyDescent="0.25">
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>5</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="1">
         <v>40</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="O8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>5</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>13.1</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="1">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="10:18" x14ac:dyDescent="0.25">
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>6</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="1">
         <v>57</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="1">
         <v>3</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="N9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="O9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>40</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>17.899999999999999</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" s="1">
         <v>720</v>
       </c>
     </row>
     <row r="10" spans="10:18" x14ac:dyDescent="0.25">
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="1">
         <v>76</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="1">
         <v>3</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="N10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="O10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>80</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>22.3</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="1">
         <v>1780</v>
       </c>
     </row>
     <row r="11" spans="10:18" x14ac:dyDescent="0.25">
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>8</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="1">
         <v>89</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="1">
         <v>3.5</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="N11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="O11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>30</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>25.9</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" s="1">
         <v>780</v>
       </c>
     </row>
     <row r="12" spans="10:18" x14ac:dyDescent="0.25">
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>9</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="1">
         <v>100</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="N12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="O12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>42.3</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="13" spans="10:18" x14ac:dyDescent="0.25">
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>10</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="1">
         <v>50</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N13" s="3" t="s">
+      <c r="N13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="O13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>1.65</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>39.5</v>
       </c>
-      <c r="R13" s="2">
+      <c r="R13" s="1">
         <v>70</v>
       </c>
     </row>
@@ -1155,7 +1145,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2C81111-BE9E-4DEB-85EF-50EEFFFA400D}">
-  <dimension ref="H1:S7"/>
+  <dimension ref="H1:S5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -1169,166 +1159,160 @@
   </cols>
   <sheetData>
     <row r="1" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="5" t="s">
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="6" t="s">
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="7"/>
-      <c r="S1" s="8"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="10"/>
     </row>
     <row r="2" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="3" t="s">
+      <c r="L2" s="4"/>
+      <c r="M2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="3" t="s">
+      <c r="P2" s="4"/>
+      <c r="Q2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>1</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>168</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="1">
         <v>56</v>
       </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="3">
+      <c r="L3" s="4"/>
+      <c r="M3" s="2">
         <v>1</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="1">
         <v>197</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="1">
         <v>5</v>
       </c>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="3">
+      <c r="P3" s="4"/>
+      <c r="Q3" s="2">
         <v>1</v>
       </c>
-      <c r="R3" s="10">
+      <c r="R3" s="1">
         <v>220</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>2</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>159</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="1">
         <v>48</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="3">
+      <c r="L4" s="4"/>
+      <c r="M4" s="2">
         <v>2</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="1">
         <v>178</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="1">
         <v>4</v>
       </c>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="3">
+      <c r="P4" s="4"/>
+      <c r="Q4" s="2">
         <v>2</v>
       </c>
-      <c r="R4" s="10">
+      <c r="R4" s="1">
         <v>263</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>3</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>164</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="1">
         <v>60</v>
       </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="3">
+      <c r="L5" s="4"/>
+      <c r="M5" s="2">
         <v>3</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="1">
         <v>159</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="1">
         <v>3</v>
       </c>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="3">
+      <c r="P5" s="4"/>
+      <c r="Q5" s="2">
         <v>3</v>
       </c>
-      <c r="R5" s="10">
+      <c r="R5" s="1">
         <v>306</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="8:19" x14ac:dyDescent="0.25">
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1343,7 +1327,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{908E707F-5DEF-440C-835B-FD9B50892F80}">
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="11" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
@@ -1354,243 +1338,242 @@
     <col min="17" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>3</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="6" t="s">
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="Q1" s="8"/>
-      <c r="S1" s="1"/>
-    </row>
-    <row r="2" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K2" s="12" t="s">
+      <c r="Q1" s="10"/>
+    </row>
+    <row r="2" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="9"/>
-      <c r="P2" s="13" t="s">
+      <c r="O2" s="4"/>
+      <c r="P2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K3" s="3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K3" s="2">
         <v>1</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="6">
         <v>32</v>
       </c>
-      <c r="O3" s="9"/>
-      <c r="P3" s="13">
+      <c r="O3" s="4"/>
+      <c r="P3" s="6">
         <v>32</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>212</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K4" s="3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K4" s="2">
         <v>2</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="6">
         <v>33</v>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="13">
+      <c r="O4" s="4"/>
+      <c r="P4" s="6">
         <v>33</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K5" s="3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K5" s="2">
         <v>3</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="6">
         <v>35</v>
       </c>
-      <c r="O5" s="9"/>
-      <c r="P5" s="13">
+      <c r="O5" s="4"/>
+      <c r="P5" s="6">
         <v>35</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>311</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K7" s="5" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K7" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K8" s="14" t="s">
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K8" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="O8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="11"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K9" s="14">
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K9" s="7">
         <v>1</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>1</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="1">
         <v>1996</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O9" s="1">
         <v>1</v>
       </c>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K10" s="14">
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K10" s="7">
         <v>2</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <v>2</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="1">
         <v>1992</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10" s="1">
         <v>1</v>
       </c>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K11" s="14">
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K11" s="7">
         <v>3</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="2">
         <v>1</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="1">
         <v>1995</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11" s="1">
         <v>2</v>
       </c>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K12" s="14">
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K12" s="7">
         <v>4</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="2">
         <v>2</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="1">
         <v>1997</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="1">
         <v>2</v>
       </c>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>49</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="7">
         <v>5</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="2">
         <v>2</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N13" s="2">
+      <c r="N13" s="1">
         <v>1999</v>
       </c>
-      <c r="O13" s="2">
+      <c r="O13" s="1">
         <v>3</v>
       </c>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
